--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CD0D7D-4A3A-43BD-B134-1E9513CFE03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B0F208-57DA-4805-B465-2413AB1AD9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,7 +193,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -204,7 +204,7 @@
     <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -225,10 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1690,7 +1687,7 @@
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="6" t="s">

--- a/- Resultados.xlsx
+++ b/- Resultados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\HNN-to-Content-Based-Hash-Retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B0F208-57DA-4805-B465-2413AB1AD9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D43F5CA-1B1B-469E-9456-68DC840EA2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,15 +1375,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>428626</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>180976</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
